--- a/data/raw/required_reserves/required_reserves_table.xlsx
+++ b/data/raw/required_reserves/required_reserves_table.xlsx
@@ -9,18 +9,18 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8610"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8610" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Обязательные резервы" sheetId="2" r:id="rId1"/>
     <sheet name="ОР_график" sheetId="6" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="152511"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="630" uniqueCount="630">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="632" uniqueCount="632">
   <si>
     <t>10.12.2009-10.01.2010</t>
   </si>
@@ -2231,11 +2231,17 @@
   <si>
     <t>16.04.2026 — 20.04.2026</t>
   </si>
+  <si>
+    <t>13.05.2026-09.06.2026</t>
+  </si>
+  <si>
+    <t>20.05.2026 — 22.05.2026</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <numFmts count="3">
     <numFmt numFmtId="164" formatCode="0.0"/>
     <numFmt numFmtId="165" formatCode="[$-419]mmmm\ yyyy;@"/>
@@ -2713,14 +2719,23 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -2756,15 +2771,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -2789,7 +2795,7 @@
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <c:date1904 val="0"/>
   <c:lang val="ru-RU"/>
   <c:roundedCorners val="0"/>
@@ -2866,7 +2872,7 @@
             <c:idx val="55"/>
             <c:invertIfNegative val="0"/>
             <c:bubble3D val="0"/>
-            <c:extLst>
+            <c:extLst xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                 <c16:uniqueId val="{00000000-3802-45C6-A5B7-E30AE7B65A00}"/>
               </c:ext>
@@ -2876,7 +2882,7 @@
             <c:idx val="56"/>
             <c:invertIfNegative val="0"/>
             <c:bubble3D val="0"/>
-            <c:extLst>
+            <c:extLst xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                 <c16:uniqueId val="{00000001-D2B1-446A-A792-206AD4FE9158}"/>
               </c:ext>
@@ -2886,7 +2892,7 @@
             <c:idx val="57"/>
             <c:invertIfNegative val="0"/>
             <c:bubble3D val="0"/>
-            <c:extLst>
+            <c:extLst xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                 <c16:uniqueId val="{00000002-D2B1-446A-A792-206AD4FE9158}"/>
               </c:ext>
@@ -2896,7 +2902,7 @@
             <c:idx val="58"/>
             <c:invertIfNegative val="0"/>
             <c:bubble3D val="0"/>
-            <c:extLst>
+            <c:extLst xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                 <c16:uniqueId val="{00000003-D2B1-446A-A792-206AD4FE9158}"/>
               </c:ext>
@@ -2906,7 +2912,7 @@
             <c:idx val="60"/>
             <c:invertIfNegative val="0"/>
             <c:bubble3D val="0"/>
-            <c:extLst>
+            <c:extLst xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                 <c16:uniqueId val="{00000004-D2B1-446A-A792-206AD4FE9158}"/>
               </c:ext>
@@ -2916,7 +2922,7 @@
             <c:idx val="61"/>
             <c:invertIfNegative val="0"/>
             <c:bubble3D val="0"/>
-            <c:extLst>
+            <c:extLst xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                 <c16:uniqueId val="{00000005-D2B1-446A-A792-206AD4FE9158}"/>
               </c:ext>
@@ -2926,7 +2932,7 @@
             <c:idx val="62"/>
             <c:invertIfNegative val="0"/>
             <c:bubble3D val="0"/>
-            <c:extLst>
+            <c:extLst xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                 <c16:uniqueId val="{00000006-D2B1-446A-A792-206AD4FE9158}"/>
               </c:ext>
@@ -2936,7 +2942,7 @@
             <c:idx val="63"/>
             <c:invertIfNegative val="0"/>
             <c:bubble3D val="0"/>
-            <c:extLst>
+            <c:extLst xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                 <c16:uniqueId val="{00000007-D2B1-446A-A792-206AD4FE9158}"/>
               </c:ext>
@@ -2946,7 +2952,7 @@
             <c:idx val="64"/>
             <c:invertIfNegative val="0"/>
             <c:bubble3D val="0"/>
-            <c:extLst>
+            <c:extLst xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                 <c16:uniqueId val="{00000008-D2B1-446A-A792-206AD4FE9158}"/>
               </c:ext>
@@ -2956,7 +2962,7 @@
             <c:idx val="65"/>
             <c:invertIfNegative val="0"/>
             <c:bubble3D val="0"/>
-            <c:extLst>
+            <c:extLst xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                 <c16:uniqueId val="{00000009-D2B1-446A-A792-206AD4FE9158}"/>
               </c:ext>
@@ -2966,7 +2972,7 @@
             <c:idx val="66"/>
             <c:invertIfNegative val="0"/>
             <c:bubble3D val="0"/>
-            <c:extLst>
+            <c:extLst xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                 <c16:uniqueId val="{0000000A-D2B1-446A-A792-206AD4FE9158}"/>
               </c:ext>
@@ -2976,7 +2982,7 @@
             <c:idx val="67"/>
             <c:invertIfNegative val="0"/>
             <c:bubble3D val="0"/>
-            <c:extLst>
+            <c:extLst xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                 <c16:uniqueId val="{0000000B-D2B1-446A-A792-206AD4FE9158}"/>
               </c:ext>
@@ -2986,7 +2992,7 @@
             <c:idx val="70"/>
             <c:invertIfNegative val="0"/>
             <c:bubble3D val="0"/>
-            <c:extLst>
+            <c:extLst xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                 <c16:uniqueId val="{0000000C-D2B1-446A-A792-206AD4FE9158}"/>
               </c:ext>
@@ -2996,7 +3002,7 @@
             <c:idx val="71"/>
             <c:invertIfNegative val="0"/>
             <c:bubble3D val="0"/>
-            <c:extLst>
+            <c:extLst xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                 <c16:uniqueId val="{0000000D-D2B1-446A-A792-206AD4FE9158}"/>
               </c:ext>
@@ -3006,7 +3012,7 @@
             <c:idx val="72"/>
             <c:invertIfNegative val="0"/>
             <c:bubble3D val="0"/>
-            <c:extLst>
+            <c:extLst xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                 <c16:uniqueId val="{0000000F-D2B1-446A-A792-206AD4FE9158}"/>
               </c:ext>
@@ -3016,7 +3022,7 @@
             <c:idx val="75"/>
             <c:invertIfNegative val="0"/>
             <c:bubble3D val="0"/>
-            <c:extLst>
+            <c:extLst xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                 <c16:uniqueId val="{0000002D-48B3-4E38-9E7E-586D28CA32A6}"/>
               </c:ext>
@@ -3026,7 +3032,7 @@
             <c:idx val="76"/>
             <c:invertIfNegative val="0"/>
             <c:bubble3D val="0"/>
-            <c:extLst>
+            <c:extLst xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                 <c16:uniqueId val="{00000024-150C-491F-9DF9-9A57D914DB91}"/>
               </c:ext>
@@ -3036,7 +3042,7 @@
             <c:idx val="77"/>
             <c:invertIfNegative val="0"/>
             <c:bubble3D val="0"/>
-            <c:extLst>
+            <c:extLst xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                 <c16:uniqueId val="{0000002E-0CA4-4CB1-9089-ED643C70F79F}"/>
               </c:ext>
@@ -3046,7 +3052,7 @@
             <c:idx val="78"/>
             <c:invertIfNegative val="0"/>
             <c:bubble3D val="0"/>
-            <c:extLst>
+            <c:extLst xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                 <c16:uniqueId val="{00000014-EA58-4A05-B426-759B544B70F5}"/>
               </c:ext>
@@ -3064,7 +3070,7 @@
                 <a:noFill/>
               </a:ln>
             </c:spPr>
-            <c:extLst>
+            <c:extLst xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                 <c16:uniqueId val="{0000002D-8A35-4563-A20D-468520A124F1}"/>
               </c:ext>
@@ -3074,7 +3080,7 @@
             <c:idx val="80"/>
             <c:invertIfNegative val="0"/>
             <c:bubble3D val="0"/>
-            <c:extLst>
+            <c:extLst xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                 <c16:uniqueId val="{0000003E-06B4-4A6C-826B-CABAE623226A}"/>
               </c:ext>
@@ -3084,7 +3090,7 @@
             <c:idx val="81"/>
             <c:invertIfNegative val="0"/>
             <c:bubble3D val="0"/>
-            <c:extLst>
+            <c:extLst xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                 <c16:uniqueId val="{00000035-3E52-4B48-B5C0-4432841545C0}"/>
               </c:ext>
@@ -3094,7 +3100,7 @@
             <c:idx val="82"/>
             <c:invertIfNegative val="0"/>
             <c:bubble3D val="0"/>
-            <c:extLst>
+            <c:extLst xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                 <c16:uniqueId val="{00000033-D628-467F-AFCA-0F3CA4215990}"/>
               </c:ext>
@@ -3104,7 +3110,7 @@
             <c:idx val="83"/>
             <c:invertIfNegative val="0"/>
             <c:bubble3D val="0"/>
-            <c:extLst>
+            <c:extLst xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                 <c16:uniqueId val="{00000043-F6CC-4139-8D3D-CA3B1D3FAD80}"/>
               </c:ext>
@@ -3114,7 +3120,7 @@
             <c:idx val="84"/>
             <c:invertIfNegative val="0"/>
             <c:bubble3D val="0"/>
-            <c:extLst>
+            <c:extLst xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                 <c16:uniqueId val="{00000040-D0C8-4C58-BFFD-A7FDF11F2227}"/>
               </c:ext>
@@ -3124,7 +3130,7 @@
             <c:idx val="85"/>
             <c:invertIfNegative val="0"/>
             <c:bubble3D val="0"/>
-            <c:extLst>
+            <c:extLst xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                 <c16:uniqueId val="{00000042-38DB-4A26-B742-99DD3AA37F78}"/>
               </c:ext>
@@ -3144,7 +3150,7 @@
                 </a:solidFill>
               </a:ln>
             </c:spPr>
-            <c:extLst>
+            <c:extLst xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                 <c16:uniqueId val="{00000038-B61A-4184-84D7-6C13A3E83B49}"/>
               </c:ext>
@@ -3164,17 +3170,37 @@
                 </a:solidFill>
               </a:ln>
             </c:spPr>
-            <c:extLst>
+            <c:extLst xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                 <c16:uniqueId val="{0000003B-D683-4696-88BF-A26274583178}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
+          <c:dPt>
+            <c:idx val="88"/>
+            <c:invertIfNegative val="0"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="C00000"/>
+              </a:solidFill>
+              <a:ln>
+                <a:solidFill>
+                  <a:schemeClr val="bg1"/>
+                </a:solidFill>
+              </a:ln>
+            </c:spPr>
+            <c:extLst xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000041-B3B1-49F2-98F5-B04FBB17453D}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
           <c:cat>
             <c:strRef>
-              <c:f>'Обязательные резервы'!$A$176:$A$265</c:f>
+              <c:f>'Обязательные резервы'!$A$176:$A$266</c:f>
               <c:strCache>
-                <c:ptCount val="90"/>
+                <c:ptCount val="91"/>
                 <c:pt idx="0">
                   <c:v>09.01.2019</c:v>
                 </c:pt>
@@ -3439,7 +3465,10 @@
                 <c:pt idx="87">
                   <c:v>15.04.2026</c:v>
                 </c:pt>
-                <c:pt idx="89">
+                <c:pt idx="88">
+                  <c:v>13.05.2026</c:v>
+                </c:pt>
+                <c:pt idx="90">
                   <c:v>1 Данные по результатам регулирования обязательных резервов за отчетный период.</c:v>
                 </c:pt>
               </c:strCache>
@@ -3447,10 +3476,10 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Обязательные резервы'!$C$176:$C$264</c:f>
+              <c:f>'Обязательные резервы'!$C$176:$C$265</c:f>
               <c:numCache>
                 <c:formatCode>0.0</c:formatCode>
-                <c:ptCount val="89"/>
+                <c:ptCount val="90"/>
                 <c:pt idx="0">
                   <c:v>2258</c:v>
                 </c:pt>
@@ -3714,11 +3743,14 @@
                 </c:pt>
                 <c:pt idx="87">
                   <c:v>5315.5</c:v>
+                </c:pt>
+                <c:pt idx="88">
+                  <c:v>5280.4</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
-          <c:extLst>
+          <c:extLst xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000000-9316-413C-9BA6-95D12D21F0D7}"/>
             </c:ext>
@@ -3745,7 +3777,7 @@
             <c:idx val="55"/>
             <c:invertIfNegative val="0"/>
             <c:bubble3D val="0"/>
-            <c:extLst>
+            <c:extLst xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                 <c16:uniqueId val="{00000001-3802-45C6-A5B7-E30AE7B65A00}"/>
               </c:ext>
@@ -3755,7 +3787,7 @@
             <c:idx val="57"/>
             <c:invertIfNegative val="0"/>
             <c:bubble3D val="0"/>
-            <c:extLst>
+            <c:extLst xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                 <c16:uniqueId val="{00000011-D2B1-446A-A792-206AD4FE9158}"/>
               </c:ext>
@@ -3765,7 +3797,7 @@
             <c:idx val="58"/>
             <c:invertIfNegative val="0"/>
             <c:bubble3D val="0"/>
-            <c:extLst>
+            <c:extLst xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                 <c16:uniqueId val="{00000012-D2B1-446A-A792-206AD4FE9158}"/>
               </c:ext>
@@ -3775,7 +3807,7 @@
             <c:idx val="60"/>
             <c:invertIfNegative val="0"/>
             <c:bubble3D val="0"/>
-            <c:extLst>
+            <c:extLst xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                 <c16:uniqueId val="{00000013-D2B1-446A-A792-206AD4FE9158}"/>
               </c:ext>
@@ -3785,7 +3817,7 @@
             <c:idx val="61"/>
             <c:invertIfNegative val="0"/>
             <c:bubble3D val="0"/>
-            <c:extLst>
+            <c:extLst xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                 <c16:uniqueId val="{00000014-D2B1-446A-A792-206AD4FE9158}"/>
               </c:ext>
@@ -3795,7 +3827,7 @@
             <c:idx val="62"/>
             <c:invertIfNegative val="0"/>
             <c:bubble3D val="0"/>
-            <c:extLst>
+            <c:extLst xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                 <c16:uniqueId val="{00000015-D2B1-446A-A792-206AD4FE9158}"/>
               </c:ext>
@@ -3805,7 +3837,7 @@
             <c:idx val="63"/>
             <c:invertIfNegative val="0"/>
             <c:bubble3D val="0"/>
-            <c:extLst>
+            <c:extLst xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                 <c16:uniqueId val="{00000016-D2B1-446A-A792-206AD4FE9158}"/>
               </c:ext>
@@ -3815,7 +3847,7 @@
             <c:idx val="64"/>
             <c:invertIfNegative val="0"/>
             <c:bubble3D val="0"/>
-            <c:extLst>
+            <c:extLst xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                 <c16:uniqueId val="{00000017-D2B1-446A-A792-206AD4FE9158}"/>
               </c:ext>
@@ -3825,7 +3857,7 @@
             <c:idx val="65"/>
             <c:invertIfNegative val="0"/>
             <c:bubble3D val="0"/>
-            <c:extLst>
+            <c:extLst xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                 <c16:uniqueId val="{00000018-D2B1-446A-A792-206AD4FE9158}"/>
               </c:ext>
@@ -3835,7 +3867,7 @@
             <c:idx val="66"/>
             <c:invertIfNegative val="0"/>
             <c:bubble3D val="0"/>
-            <c:extLst>
+            <c:extLst xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                 <c16:uniqueId val="{00000019-D2B1-446A-A792-206AD4FE9158}"/>
               </c:ext>
@@ -3845,7 +3877,7 @@
             <c:idx val="67"/>
             <c:invertIfNegative val="0"/>
             <c:bubble3D val="0"/>
-            <c:extLst>
+            <c:extLst xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                 <c16:uniqueId val="{0000001A-D2B1-446A-A792-206AD4FE9158}"/>
               </c:ext>
@@ -3855,7 +3887,7 @@
             <c:idx val="70"/>
             <c:invertIfNegative val="0"/>
             <c:bubble3D val="0"/>
-            <c:extLst>
+            <c:extLst xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                 <c16:uniqueId val="{0000001B-D2B1-446A-A792-206AD4FE9158}"/>
               </c:ext>
@@ -3865,7 +3897,7 @@
             <c:idx val="71"/>
             <c:invertIfNegative val="0"/>
             <c:bubble3D val="0"/>
-            <c:extLst>
+            <c:extLst xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                 <c16:uniqueId val="{0000001C-D2B1-446A-A792-206AD4FE9158}"/>
               </c:ext>
@@ -3875,7 +3907,7 @@
             <c:idx val="72"/>
             <c:invertIfNegative val="0"/>
             <c:bubble3D val="0"/>
-            <c:extLst>
+            <c:extLst xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                 <c16:uniqueId val="{0000001E-D2B1-446A-A792-206AD4FE9158}"/>
               </c:ext>
@@ -3885,7 +3917,7 @@
             <c:idx val="75"/>
             <c:invertIfNegative val="0"/>
             <c:bubble3D val="0"/>
-            <c:extLst>
+            <c:extLst xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                 <c16:uniqueId val="{0000002C-48B3-4E38-9E7E-586D28CA32A6}"/>
               </c:ext>
@@ -3895,7 +3927,7 @@
             <c:idx val="76"/>
             <c:invertIfNegative val="0"/>
             <c:bubble3D val="0"/>
-            <c:extLst>
+            <c:extLst xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                 <c16:uniqueId val="{00000023-150C-491F-9DF9-9A57D914DB91}"/>
               </c:ext>
@@ -3905,7 +3937,7 @@
             <c:idx val="77"/>
             <c:invertIfNegative val="0"/>
             <c:bubble3D val="0"/>
-            <c:extLst>
+            <c:extLst xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                 <c16:uniqueId val="{0000002A-0CA4-4CB1-9089-ED643C70F79F}"/>
               </c:ext>
@@ -3920,7 +3952,7 @@
                 <a:srgbClr val="92D050"/>
               </a:solidFill>
             </c:spPr>
-            <c:extLst>
+            <c:extLst xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                 <c16:uniqueId val="{00000028-EA58-4A05-B426-759B544B70F5}"/>
               </c:ext>
@@ -3938,7 +3970,7 @@
                 <a:noFill/>
               </a:ln>
             </c:spPr>
-            <c:extLst>
+            <c:extLst xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                 <c16:uniqueId val="{0000002C-8A35-4563-A20D-468520A124F1}"/>
               </c:ext>
@@ -3948,7 +3980,7 @@
             <c:idx val="80"/>
             <c:invertIfNegative val="0"/>
             <c:bubble3D val="0"/>
-            <c:extLst>
+            <c:extLst xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                 <c16:uniqueId val="{0000003D-06B4-4A6C-826B-CABAE623226A}"/>
               </c:ext>
@@ -3958,7 +3990,7 @@
             <c:idx val="81"/>
             <c:invertIfNegative val="0"/>
             <c:bubble3D val="0"/>
-            <c:extLst>
+            <c:extLst xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                 <c16:uniqueId val="{00000034-3E52-4B48-B5C0-4432841545C0}"/>
               </c:ext>
@@ -3968,7 +4000,7 @@
             <c:idx val="82"/>
             <c:invertIfNegative val="0"/>
             <c:bubble3D val="0"/>
-            <c:extLst>
+            <c:extLst xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                 <c16:uniqueId val="{00000032-D628-467F-AFCA-0F3CA4215990}"/>
               </c:ext>
@@ -3978,7 +4010,7 @@
             <c:idx val="83"/>
             <c:invertIfNegative val="0"/>
             <c:bubble3D val="0"/>
-            <c:extLst>
+            <c:extLst xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                 <c16:uniqueId val="{00000042-F6CC-4139-8D3D-CA3B1D3FAD80}"/>
               </c:ext>
@@ -3988,7 +4020,7 @@
             <c:idx val="84"/>
             <c:invertIfNegative val="0"/>
             <c:bubble3D val="0"/>
-            <c:extLst>
+            <c:extLst xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                 <c16:uniqueId val="{0000003F-D0C8-4C58-BFFD-A7FDF11F2227}"/>
               </c:ext>
@@ -3998,7 +4030,7 @@
             <c:idx val="85"/>
             <c:invertIfNegative val="0"/>
             <c:bubble3D val="0"/>
-            <c:extLst>
+            <c:extLst xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                 <c16:uniqueId val="{00000041-38DB-4A26-B742-99DD3AA37F78}"/>
               </c:ext>
@@ -4008,7 +4040,7 @@
             <c:idx val="86"/>
             <c:invertIfNegative val="0"/>
             <c:bubble3D val="0"/>
-            <c:extLst>
+            <c:extLst xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                 <c16:uniqueId val="{00000037-B61A-4184-84D7-6C13A3E83B49}"/>
               </c:ext>
@@ -4026,17 +4058,37 @@
                 <a:noFill/>
               </a:ln>
             </c:spPr>
-            <c:extLst>
+            <c:extLst xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                 <c16:uniqueId val="{0000003A-D683-4696-88BF-A26274583178}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
+          <c:dPt>
+            <c:idx val="88"/>
+            <c:invertIfNegative val="0"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="92D050"/>
+              </a:solidFill>
+              <a:ln>
+                <a:solidFill>
+                  <a:schemeClr val="bg1"/>
+                </a:solidFill>
+              </a:ln>
+            </c:spPr>
+            <c:extLst xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000040-B3B1-49F2-98F5-B04FBB17453D}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
           <c:cat>
             <c:strRef>
-              <c:f>'Обязательные резервы'!$A$176:$A$265</c:f>
+              <c:f>'Обязательные резервы'!$A$176:$A$266</c:f>
               <c:strCache>
-                <c:ptCount val="90"/>
+                <c:ptCount val="91"/>
                 <c:pt idx="0">
                   <c:v>09.01.2019</c:v>
                 </c:pt>
@@ -4301,7 +4353,10 @@
                 <c:pt idx="87">
                   <c:v>15.04.2026</c:v>
                 </c:pt>
-                <c:pt idx="89">
+                <c:pt idx="88">
+                  <c:v>13.05.2026</c:v>
+                </c:pt>
+                <c:pt idx="90">
                   <c:v>1 Данные по результатам регулирования обязательных резервов за отчетный период.</c:v>
                 </c:pt>
               </c:strCache>
@@ -4309,10 +4364,10 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Обязательные резервы'!$D$176:$D$264</c:f>
+              <c:f>'Обязательные резервы'!$D$176:$D$265</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="89"/>
+                <c:ptCount val="90"/>
                 <c:pt idx="0">
                   <c:v>586.29999999999995</c:v>
                 </c:pt>
@@ -4576,11 +4631,14 @@
                 </c:pt>
                 <c:pt idx="87" formatCode="0.0">
                   <c:v>587.5</c:v>
+                </c:pt>
+                <c:pt idx="88" formatCode="0.0">
+                  <c:v>588.4</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
-          <c:extLst>
+          <c:extLst xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000001-9316-413C-9BA6-95D12D21F0D7}"/>
             </c:ext>
@@ -4596,8 +4654,8 @@
         </c:dLbls>
         <c:gapWidth val="150"/>
         <c:overlap val="100"/>
-        <c:axId val="1392582208"/>
-        <c:axId val="1392588736"/>
+        <c:axId val="207041696"/>
+        <c:axId val="207043264"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -4833,10 +4891,10 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Обязательные резервы'!$B$176:$B$264</c:f>
+              <c:f>'Обязательные резервы'!$B$176:$B$265</c:f>
               <c:numCache>
                 <c:formatCode>0.0</c:formatCode>
-                <c:ptCount val="89"/>
+                <c:ptCount val="90"/>
                 <c:pt idx="0">
                   <c:v>2331.4</c:v>
                 </c:pt>
@@ -5097,12 +5155,15 @@
                 </c:pt>
                 <c:pt idx="86">
                   <c:v>5407.2</c:v>
+                </c:pt>
+                <c:pt idx="87">
+                  <c:v>5445.4</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
           <c:smooth val="0"/>
-          <c:extLst>
+          <c:extLst xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000002-9316-413C-9BA6-95D12D21F0D7}"/>
             </c:ext>
@@ -5118,11 +5179,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="1392578400"/>
-        <c:axId val="1392586560"/>
+        <c:axId val="207043656"/>
+        <c:axId val="207042872"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="1392582208"/>
+        <c:axId val="207041696"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5132,7 +5193,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="1392588736"/>
+        <c:crossAx val="207043264"/>
         <c:crosses val="autoZero"/>
         <c:auto val="0"/>
         <c:lblAlgn val="ctr"/>
@@ -5141,7 +5202,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="1392588736"/>
+        <c:axId val="207043264"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5152,12 +5213,12 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="1392582208"/>
+        <c:crossAx val="207041696"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="1392586560"/>
+        <c:axId val="207042872"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="5000"/>
@@ -5195,12 +5256,12 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="1392578400"/>
+        <c:crossAx val="207043656"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="1392578400"/>
+        <c:axId val="207043656"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5210,7 +5271,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="1392586560"/>
+        <c:crossAx val="207042872"/>
         <c:crosses val="autoZero"/>
         <c:auto val="0"/>
         <c:lblAlgn val="ctr"/>
@@ -5264,13 +5325,13 @@
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:rowOff>6803</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>13</xdr:col>
       <xdr:colOff>468312</xdr:colOff>
       <xdr:row>23</xdr:row>
-      <xdr:rowOff>182562</xdr:rowOff>
+      <xdr:rowOff>189365</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -5584,7 +5645,7 @@
   <sheetPr codeName="Лист1">
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:L316"/>
+  <dimension ref="A1:L317"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="26.42578125" customWidth="1"/>
@@ -5601,36 +5662,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" s="3" customFormat="1" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A1" s="62" t="s">
+      <c r="A1" s="66" t="s">
         <v>410</v>
       </c>
-      <c r="B1" s="63"/>
-      <c r="C1" s="63"/>
-      <c r="D1" s="63"/>
-      <c r="E1" s="63"/>
-      <c r="F1" s="63"/>
-      <c r="G1" s="63"/>
-      <c r="H1" s="63"/>
-      <c r="I1" s="63"/>
-      <c r="J1" s="63"/>
+      <c r="B1" s="67"/>
+      <c r="C1" s="67"/>
+      <c r="D1" s="67"/>
+      <c r="E1" s="67"/>
+      <c r="F1" s="67"/>
+      <c r="G1" s="67"/>
+      <c r="H1" s="67"/>
+      <c r="I1" s="67"/>
+      <c r="J1" s="67"/>
     </row>
     <row r="2" spans="1:12" s="3" customFormat="1" ht="37.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="6"/>
-      <c r="B2" s="71" t="s">
+      <c r="B2" s="74" t="s">
         <v>561</v>
       </c>
-      <c r="C2" s="72"/>
-      <c r="D2" s="73"/>
-      <c r="E2" s="69" t="s">
+      <c r="C2" s="75"/>
+      <c r="D2" s="76"/>
+      <c r="E2" s="72" t="s">
         <v>405</v>
       </c>
-      <c r="F2" s="70"/>
-      <c r="G2" s="74" t="s">
+      <c r="F2" s="73"/>
+      <c r="G2" s="77" t="s">
         <v>244</v>
       </c>
-      <c r="H2" s="75"/>
-      <c r="I2" s="75"/>
-      <c r="J2" s="76"/>
+      <c r="H2" s="78"/>
+      <c r="I2" s="78"/>
+      <c r="J2" s="79"/>
     </row>
     <row r="3" spans="1:12" s="5" customFormat="1" ht="55.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="52" t="s">
@@ -14017,7 +14078,9 @@
       <c r="A263" s="23">
         <v>46127</v>
       </c>
-      <c r="B263" s="8"/>
+      <c r="B263" s="8">
+        <v>5445.4</v>
+      </c>
       <c r="C263" s="13">
         <v>5315.5</v>
       </c>
@@ -14043,106 +14106,123 @@
         <v>629</v>
       </c>
     </row>
-    <row r="264" spans="1:10" s="40" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A264" s="33"/>
-      <c r="B264" s="34"/>
-      <c r="C264" s="35"/>
-      <c r="D264" s="36"/>
-      <c r="E264" s="37"/>
-      <c r="F264" s="61"/>
-      <c r="G264" s="33"/>
-      <c r="H264" s="38"/>
-      <c r="I264" s="39"/>
-      <c r="J264" s="33"/>
-    </row>
-    <row r="265" spans="1:10" s="3" customFormat="1" ht="18" x14ac:dyDescent="0.25">
-      <c r="A265" s="68" t="s">
+    <row r="264" spans="1:10" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A264" s="23">
+        <v>46155</v>
+      </c>
+      <c r="B264" s="8"/>
+      <c r="C264" s="13">
+        <v>5280.4</v>
+      </c>
+      <c r="D264" s="28">
+        <v>588.4</v>
+      </c>
+      <c r="E264" s="14">
+        <v>347</v>
+      </c>
+      <c r="F264" s="60">
+        <v>347</v>
+      </c>
+      <c r="G264" s="29" t="s">
+        <v>630</v>
+      </c>
+      <c r="H264" s="7">
+        <v>28</v>
+      </c>
+      <c r="I264" s="17">
+        <v>46113</v>
+      </c>
+      <c r="J264" s="29" t="s">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="265" spans="1:10" s="40" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A265" s="33"/>
+      <c r="B265" s="34"/>
+      <c r="C265" s="35"/>
+      <c r="D265" s="36"/>
+      <c r="E265" s="37"/>
+      <c r="F265" s="61"/>
+      <c r="G265" s="33"/>
+      <c r="H265" s="38"/>
+      <c r="I265" s="39"/>
+      <c r="J265" s="33"/>
+    </row>
+    <row r="266" spans="1:10" s="3" customFormat="1" ht="18" x14ac:dyDescent="0.25">
+      <c r="A266" s="71" t="s">
         <v>407</v>
       </c>
-      <c r="B265" s="68"/>
-      <c r="C265" s="68"/>
-      <c r="D265" s="68"/>
-      <c r="E265" s="68"/>
-      <c r="F265" s="68"/>
-      <c r="G265" s="30"/>
-    </row>
-    <row r="266" spans="1:10" ht="79.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A266" s="66" t="s">
+      <c r="B266" s="71"/>
+      <c r="C266" s="71"/>
+      <c r="D266" s="71"/>
+      <c r="E266" s="71"/>
+      <c r="F266" s="71"/>
+      <c r="G266" s="30"/>
+    </row>
+    <row r="267" spans="1:10" ht="79.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A267" s="69" t="s">
         <v>408</v>
       </c>
-      <c r="B266" s="67"/>
-      <c r="C266" s="67"/>
-      <c r="D266" s="67"/>
-      <c r="E266" s="67"/>
-      <c r="F266" s="67"/>
-      <c r="G266" s="19"/>
-      <c r="H266" s="26"/>
-      <c r="I266" s="26"/>
-      <c r="J266" s="3"/>
-    </row>
-    <row r="267" spans="1:10" s="3" customFormat="1" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A267" s="79" t="s">
+      <c r="B267" s="70"/>
+      <c r="C267" s="70"/>
+      <c r="D267" s="70"/>
+      <c r="E267" s="70"/>
+      <c r="F267" s="70"/>
+      <c r="G267" s="19"/>
+      <c r="H267" s="26"/>
+      <c r="I267" s="26"/>
+      <c r="J267" s="3"/>
+    </row>
+    <row r="268" spans="1:10" s="3" customFormat="1" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A268" s="63" t="s">
         <v>555</v>
       </c>
-      <c r="B267" s="79"/>
-      <c r="C267" s="79"/>
-      <c r="D267" s="79"/>
-      <c r="E267" s="79"/>
-      <c r="F267" s="79"/>
-      <c r="H267" s="77"/>
-      <c r="I267" s="77"/>
-    </row>
-    <row r="268" spans="1:10" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A268" s="64" t="s">
+      <c r="B268" s="63"/>
+      <c r="C268" s="63"/>
+      <c r="D268" s="63"/>
+      <c r="E268" s="63"/>
+      <c r="F268" s="63"/>
+      <c r="H268" s="64"/>
+      <c r="I268" s="64"/>
+    </row>
+    <row r="269" spans="1:10" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A269" s="65" t="s">
         <v>556</v>
       </c>
-      <c r="B268" s="64"/>
-      <c r="C268" s="64"/>
-      <c r="D268" s="64"/>
-      <c r="E268" s="64"/>
-      <c r="F268" s="64"/>
-      <c r="G268" s="45"/>
-    </row>
-    <row r="269" spans="1:10" s="3" customFormat="1" ht="17.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A269" s="64" t="s">
+      <c r="B269" s="65"/>
+      <c r="C269" s="65"/>
+      <c r="D269" s="65"/>
+      <c r="E269" s="65"/>
+      <c r="F269" s="65"/>
+      <c r="G269" s="45"/>
+    </row>
+    <row r="270" spans="1:10" s="3" customFormat="1" ht="17.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A270" s="65" t="s">
         <v>557</v>
       </c>
-      <c r="B269" s="64"/>
-      <c r="C269" s="64"/>
-      <c r="D269" s="64"/>
-      <c r="E269" s="64"/>
-      <c r="F269" s="64"/>
-      <c r="G269" s="45"/>
-      <c r="H269" s="44"/>
-    </row>
-    <row r="270" spans="1:10" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A270" s="64" t="s">
+      <c r="B270" s="65"/>
+      <c r="C270" s="65"/>
+      <c r="D270" s="65"/>
+      <c r="E270" s="65"/>
+      <c r="F270" s="65"/>
+      <c r="G270" s="45"/>
+      <c r="H270" s="44"/>
+    </row>
+    <row r="271" spans="1:10" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A271" s="65" t="s">
         <v>558</v>
       </c>
-      <c r="B270" s="64"/>
-      <c r="C270" s="64"/>
-      <c r="D270" s="64"/>
-      <c r="E270" s="64"/>
-      <c r="F270" s="64"/>
-      <c r="H270" s="77"/>
-      <c r="I270" s="77"/>
-    </row>
-    <row r="271" spans="1:10" ht="51" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A271" s="64" t="s">
+      <c r="B271" s="65"/>
+      <c r="C271" s="65"/>
+      <c r="D271" s="65"/>
+      <c r="E271" s="65"/>
+      <c r="F271" s="65"/>
+      <c r="H271" s="64"/>
+      <c r="I271" s="64"/>
+    </row>
+    <row r="272" spans="1:10" ht="51" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A272" s="65" t="s">
         <v>559</v>
-      </c>
-      <c r="B271" s="64"/>
-      <c r="C271" s="64"/>
-      <c r="D271" s="64"/>
-      <c r="E271" s="64"/>
-      <c r="F271" s="64"/>
-      <c r="G271" s="19"/>
-      <c r="H271" s="77"/>
-      <c r="I271" s="77"/>
-    </row>
-    <row r="272" spans="1:10" ht="18" x14ac:dyDescent="0.25">
-      <c r="A272" s="65" t="s">
-        <v>560</v>
       </c>
       <c r="B272" s="65"/>
       <c r="C272" s="65"/>
@@ -14150,199 +14230,212 @@
       <c r="E272" s="65"/>
       <c r="F272" s="65"/>
       <c r="G272" s="19"/>
-      <c r="H272" s="77"/>
-      <c r="I272" s="77"/>
+      <c r="H272" s="64"/>
+      <c r="I272" s="64"/>
     </row>
     <row r="273" spans="1:9" ht="18" x14ac:dyDescent="0.25">
-      <c r="A273" s="78"/>
-      <c r="B273" s="78"/>
-      <c r="C273" s="78"/>
-      <c r="D273" s="78"/>
-      <c r="E273" s="78"/>
-      <c r="F273" s="78"/>
-      <c r="H273" s="46"/>
-    </row>
-    <row r="274" spans="1:9" s="3" customFormat="1" ht="18" x14ac:dyDescent="0.25">
-      <c r="A274" s="64"/>
-      <c r="B274" s="78"/>
-      <c r="C274" s="78"/>
-      <c r="D274" s="78"/>
-      <c r="E274" s="78"/>
-      <c r="F274" s="78"/>
-      <c r="H274" s="47"/>
-      <c r="I274"/>
-    </row>
-    <row r="275" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A275" s="41"/>
-      <c r="B275" s="2"/>
-      <c r="C275" s="2"/>
+      <c r="A273" s="68" t="s">
+        <v>560</v>
+      </c>
+      <c r="B273" s="68"/>
+      <c r="C273" s="68"/>
+      <c r="D273" s="68"/>
+      <c r="E273" s="68"/>
+      <c r="F273" s="68"/>
+      <c r="G273" s="19"/>
+      <c r="H273" s="64"/>
+      <c r="I273" s="64"/>
+    </row>
+    <row r="274" spans="1:9" ht="18" x14ac:dyDescent="0.25">
+      <c r="A274" s="62"/>
+      <c r="B274" s="62"/>
+      <c r="C274" s="62"/>
+      <c r="D274" s="62"/>
+      <c r="E274" s="62"/>
+      <c r="F274" s="62"/>
+      <c r="H274" s="46"/>
+    </row>
+    <row r="275" spans="1:9" s="3" customFormat="1" ht="18" x14ac:dyDescent="0.25">
+      <c r="A275" s="65"/>
+      <c r="B275" s="62"/>
+      <c r="C275" s="62"/>
+      <c r="D275" s="62"/>
+      <c r="E275" s="62"/>
+      <c r="F275" s="62"/>
+      <c r="H275" s="47"/>
+      <c r="I275"/>
     </row>
     <row r="276" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A276" s="1"/>
+      <c r="A276" s="41"/>
       <c r="B276" s="2"/>
       <c r="C276" s="2"/>
-      <c r="H276" s="4"/>
     </row>
     <row r="277" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A277" s="1"/>
       <c r="B277" s="2"/>
       <c r="C277" s="2"/>
+      <c r="H277" s="4"/>
     </row>
     <row r="278" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A278" s="1"/>
       <c r="B278" s="2"/>
       <c r="C278" s="2"/>
-      <c r="H278" s="4"/>
     </row>
     <row r="279" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A279" s="1"/>
       <c r="B279" s="2"/>
       <c r="C279" s="2"/>
+      <c r="H279" s="4"/>
     </row>
     <row r="280" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A280" s="1"/>
       <c r="B280" s="2"/>
       <c r="C280" s="2"/>
-      <c r="H280" s="4"/>
     </row>
     <row r="281" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A281" s="1"/>
       <c r="B281" s="2"/>
       <c r="C281" s="2"/>
+      <c r="H281" s="4"/>
     </row>
     <row r="282" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A282" s="1"/>
       <c r="B282" s="2"/>
       <c r="C282" s="2"/>
-      <c r="H282" s="4"/>
     </row>
     <row r="283" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A283" s="1"/>
       <c r="B283" s="2"/>
       <c r="C283" s="2"/>
+      <c r="H283" s="4"/>
     </row>
     <row r="284" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A284" s="1"/>
       <c r="B284" s="2"/>
       <c r="C284" s="2"/>
-      <c r="H284" s="4"/>
     </row>
     <row r="285" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A285" s="1"/>
       <c r="B285" s="2"/>
       <c r="C285" s="2"/>
+      <c r="H285" s="4"/>
     </row>
     <row r="286" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A286" s="1"/>
       <c r="B286" s="2"/>
       <c r="C286" s="2"/>
-      <c r="H286" s="4"/>
     </row>
     <row r="287" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A287" s="1"/>
       <c r="B287" s="2"/>
       <c r="C287" s="2"/>
+      <c r="H287" s="4"/>
     </row>
     <row r="288" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A288" s="1"/>
       <c r="B288" s="2"/>
       <c r="C288" s="2"/>
-      <c r="H288" s="4"/>
     </row>
     <row r="289" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A289" s="1"/>
       <c r="B289" s="2"/>
       <c r="C289" s="2"/>
+      <c r="H289" s="4"/>
     </row>
     <row r="290" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A290" s="1"/>
       <c r="B290" s="2"/>
       <c r="C290" s="2"/>
-      <c r="H290" s="4"/>
     </row>
     <row r="291" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A291" s="1"/>
       <c r="B291" s="2"/>
       <c r="C291" s="2"/>
+      <c r="H291" s="4"/>
     </row>
     <row r="292" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A292" s="1"/>
       <c r="B292" s="2"/>
       <c r="C292" s="2"/>
-      <c r="H292" s="4"/>
     </row>
     <row r="293" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A293" s="1"/>
       <c r="B293" s="2"/>
       <c r="C293" s="2"/>
+      <c r="H293" s="4"/>
     </row>
     <row r="294" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A294" s="1"/>
       <c r="B294" s="2"/>
       <c r="C294" s="2"/>
-      <c r="H294" s="4"/>
     </row>
     <row r="295" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A295" s="1"/>
       <c r="B295" s="2"/>
       <c r="C295" s="2"/>
+      <c r="H295" s="4"/>
     </row>
     <row r="296" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A296" s="1"/>
       <c r="B296" s="2"/>
       <c r="C296" s="2"/>
-      <c r="H296" s="4"/>
-    </row>
-    <row r="298" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A298" s="1"/>
-      <c r="H298" s="4"/>
-    </row>
-    <row r="300" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A300" s="1"/>
-      <c r="H300" s="4"/>
-    </row>
-    <row r="302" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A302" s="1"/>
-      <c r="H302" s="4"/>
-    </row>
-    <row r="304" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A304" s="1"/>
-      <c r="H304" s="4"/>
-    </row>
-    <row r="306" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A306" s="1"/>
-      <c r="H306" s="4"/>
-    </row>
-    <row r="308" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A308" s="1"/>
-      <c r="H308" s="4"/>
-    </row>
-    <row r="310" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A310" s="1"/>
-      <c r="H310" s="4"/>
-    </row>
-    <row r="312" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A312" s="1"/>
-      <c r="H312" s="4"/>
-    </row>
-    <row r="314" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A314" s="1"/>
-      <c r="H314" s="4"/>
-    </row>
-    <row r="316" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A316" s="1"/>
-      <c r="H316" s="4"/>
+    </row>
+    <row r="297" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A297" s="1"/>
+      <c r="B297" s="2"/>
+      <c r="C297" s="2"/>
+      <c r="H297" s="4"/>
+    </row>
+    <row r="299" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A299" s="1"/>
+      <c r="H299" s="4"/>
+    </row>
+    <row r="301" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A301" s="1"/>
+      <c r="H301" s="4"/>
+    </row>
+    <row r="303" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A303" s="1"/>
+      <c r="H303" s="4"/>
+    </row>
+    <row r="305" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A305" s="1"/>
+      <c r="H305" s="4"/>
+    </row>
+    <row r="307" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A307" s="1"/>
+      <c r="H307" s="4"/>
+    </row>
+    <row r="309" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A309" s="1"/>
+      <c r="H309" s="4"/>
+    </row>
+    <row r="311" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A311" s="1"/>
+      <c r="H311" s="4"/>
+    </row>
+    <row r="313" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A313" s="1"/>
+      <c r="H313" s="4"/>
+    </row>
+    <row r="315" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A315" s="1"/>
+      <c r="H315" s="4"/>
+    </row>
+    <row r="317" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A317" s="1"/>
+      <c r="H317" s="4"/>
     </row>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A269:F269"/>
+    <mergeCell ref="A272:F272"/>
     <mergeCell ref="A273:F273"/>
+    <mergeCell ref="A271:F271"/>
     <mergeCell ref="A267:F267"/>
-    <mergeCell ref="H267:I267"/>
-    <mergeCell ref="H272:I272"/>
-    <mergeCell ref="A274:F274"/>
-    <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A268:F268"/>
-    <mergeCell ref="A271:F271"/>
-    <mergeCell ref="A272:F272"/>
-    <mergeCell ref="A270:F270"/>
     <mergeCell ref="A266:F266"/>
-    <mergeCell ref="A265:F265"/>
     <mergeCell ref="E2:F2"/>
     <mergeCell ref="B2:D2"/>
     <mergeCell ref="G2:J2"/>
-    <mergeCell ref="A269:F269"/>
-    <mergeCell ref="H270:I270"/>
+    <mergeCell ref="A270:F270"/>
     <mergeCell ref="H271:I271"/>
+    <mergeCell ref="H272:I272"/>
+    <mergeCell ref="A274:F274"/>
+    <mergeCell ref="A268:F268"/>
+    <mergeCell ref="H268:I268"/>
+    <mergeCell ref="H273:I273"/>
+    <mergeCell ref="A275:F275"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="11" orientation="landscape" r:id="rId1"/>
